--- a/Output/PowerPoint_Figures/Fig_3/Fig_3b_Dactinomycin_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3b_Dactinomycin_data.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,201 +420,201 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
+      <c r="B1" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>35</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>38</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>41</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>46</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>49</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>51</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>54</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>56</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>59</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>62</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>64</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>67</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>70</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>72</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>75</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>78</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>80</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>83</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>86</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>88</v>
       </c>
-      <c r="AG1" s="1" t="n">
+      <c r="AG1" t="n">
         <v>91</v>
       </c>
-      <c r="AH1" s="1" t="n">
+      <c r="AH1" t="n">
         <v>94</v>
       </c>
-      <c r="AI1" s="1" t="n">
+      <c r="AI1" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1.5.1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.55138232685458</v>
+        <v>21.55138232685471</v>
       </c>
       <c r="C2" t="n">
-        <v>26.46562931895072</v>
+        <v>26.46562931895091</v>
       </c>
       <c r="D2" t="n">
-        <v>31.35683487208517</v>
+        <v>30.99255358967835</v>
       </c>
       <c r="E2" t="n">
-        <v>36.22136579513044</v>
+        <v>35.38621364920659</v>
       </c>
       <c r="F2" t="n">
-        <v>41.062769164963</v>
+        <v>41.06276916496333</v>
       </c>
       <c r="G2" t="n">
-        <v>45.9083592579968</v>
+        <v>45.90835925799718</v>
       </c>
       <c r="H2" t="n">
-        <v>50.92101269797291</v>
+        <v>50.92101269797338</v>
       </c>
       <c r="I2" t="n">
-        <v>57.83028205252658</v>
+        <v>57.83028205252751</v>
       </c>
       <c r="J2" t="n">
-        <v>67.34714253755017</v>
+        <v>67.34714253755082</v>
       </c>
       <c r="K2" t="n">
-        <v>70.80299828803402</v>
+        <v>70.80299828803385</v>
       </c>
       <c r="L2" t="n">
-        <v>71.43706300139111</v>
+        <v>71.43706300139102</v>
       </c>
       <c r="M2" t="n">
-        <v>71.89008768460879</v>
+        <v>71.89008768460872</v>
       </c>
       <c r="N2" t="n">
-        <v>72.25901253107187</v>
+        <v>72.25901253107183</v>
       </c>
       <c r="O2" t="n">
-        <v>72.59833653289246</v>
+        <v>72.59833653289242</v>
       </c>
       <c r="P2" t="n">
-        <v>72.93104985900223</v>
+        <v>72.93104985900224</v>
       </c>
       <c r="Q2" t="n">
-        <v>73.24917948202601</v>
+        <v>73.24917948202599</v>
       </c>
       <c r="R2" t="n">
         <v>73.5368122342269</v>
       </c>
       <c r="S2" t="n">
-        <v>73.79259834123557</v>
+        <v>73.79259834123556</v>
       </c>
       <c r="T2" t="n">
-        <v>74.03799619074091</v>
+        <v>74.03799619074093</v>
       </c>
       <c r="U2" t="n">
-        <v>74.28397050728151</v>
+        <v>74.28397050728152</v>
       </c>
       <c r="V2" t="n">
         <v>74.53113599871388</v>
       </c>
       <c r="W2" t="n">
-        <v>74.77850244634347</v>
+        <v>74.7785024463435</v>
       </c>
       <c r="X2" t="n">
-        <v>75.00211932477899</v>
+        <v>75.002119324779</v>
       </c>
       <c r="Y2" t="n">
-        <v>75.18582668365093</v>
+        <v>75.18582668365096</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.35030588520729</v>
+        <v>75.35030588520732</v>
       </c>
       <c r="AA2" t="n">
-        <v>75.52880184585246</v>
+        <v>75.52880184585248</v>
       </c>
       <c r="AB2" t="n">
-        <v>75.7307152197334</v>
+        <v>75.73071521973343</v>
       </c>
       <c r="AC2" t="n">
-        <v>75.95172818873225</v>
+        <v>75.95172818873228</v>
       </c>
       <c r="AD2" t="n">
-        <v>76.1566546146133</v>
+        <v>76.15665461461333</v>
       </c>
       <c r="AE2" t="n">
         <v>76.35578684919025</v>
@@ -635,41 +623,41 @@
         <v>76.55448332821675</v>
       </c>
       <c r="AG2" t="n">
-        <v>76.7566959245037</v>
+        <v>76.75669592450384</v>
       </c>
       <c r="AH2" t="n">
-        <v>76.96412922385419</v>
+        <v>76.96412922385436</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.17580433961463</v>
+        <v>77.17580433961456</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.08321547829444</v>
+        <v>30.52365711857453</v>
       </c>
       <c r="C3" t="n">
-        <v>34.47999782553417</v>
+        <v>32.74431807041888</v>
       </c>
       <c r="D3" t="n">
-        <v>37.80815229444102</v>
+        <v>35.79141740749161</v>
       </c>
       <c r="E3" t="n">
-        <v>41.06348197995359</v>
+        <v>39.63471181521221</v>
       </c>
       <c r="F3" t="n">
-        <v>44.24513745695647</v>
+        <v>44.24513745695636</v>
       </c>
       <c r="G3" t="n">
-        <v>47.35266396831612</v>
+        <v>47.35266396831606</v>
       </c>
       <c r="H3" t="n">
-        <v>50.37555039936283</v>
+        <v>50.37555039936281</v>
       </c>
       <c r="I3" t="n">
         <v>53.28768723596281</v>
@@ -678,55 +666,55 @@
         <v>55.86418885287215</v>
       </c>
       <c r="K3" t="n">
-        <v>58.30588315525902</v>
+        <v>58.305883155259</v>
       </c>
       <c r="L3" t="n">
-        <v>60.71100145226265</v>
+        <v>60.71100145226261</v>
       </c>
       <c r="M3" t="n">
-        <v>63.70800439623709</v>
+        <v>63.70800439623712</v>
       </c>
       <c r="N3" t="n">
-        <v>68.34800106048428</v>
+        <v>68.34800106048434</v>
       </c>
       <c r="O3" t="n">
-        <v>70.34187267542455</v>
+        <v>70.34187267542461</v>
       </c>
       <c r="P3" t="n">
-        <v>70.60585649074024</v>
+        <v>70.60585649074028</v>
       </c>
       <c r="Q3" t="n">
-        <v>70.84461563101797</v>
+        <v>70.84461563101802</v>
       </c>
       <c r="R3" t="n">
-        <v>71.06204901522491</v>
+        <v>71.06204901522487</v>
       </c>
       <c r="S3" t="n">
-        <v>71.24347832251809</v>
+        <v>71.24347832251804</v>
       </c>
       <c r="T3" t="n">
         <v>71.38686376222792</v>
       </c>
       <c r="U3" t="n">
-        <v>71.51008660702536</v>
+        <v>71.51008660702534</v>
       </c>
       <c r="V3" t="n">
-        <v>71.62814598181686</v>
+        <v>71.62814598181687</v>
       </c>
       <c r="W3" t="n">
-        <v>71.73704747158803</v>
+        <v>71.73704747158801</v>
       </c>
       <c r="X3" t="n">
         <v>71.83292211520865</v>
       </c>
       <c r="Y3" t="n">
-        <v>71.91806827684704</v>
+        <v>71.91806827684702</v>
       </c>
       <c r="Z3" t="n">
         <v>71.99788091429885</v>
       </c>
       <c r="AA3" t="n">
-        <v>72.08203498112545</v>
+        <v>72.08203498112546</v>
       </c>
       <c r="AB3" t="n">
         <v>72.17995237799659</v>
@@ -735,180 +723,180 @@
         <v>72.29896283469476</v>
       </c>
       <c r="AD3" t="n">
-        <v>72.41262648275119</v>
+        <v>72.41262648275118</v>
       </c>
       <c r="AE3" t="n">
-        <v>72.52451796641813</v>
+        <v>72.52451796641812</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.63671118480394</v>
+        <v>72.63671118480386</v>
       </c>
       <c r="AG3" t="n">
-        <v>72.75004211774274</v>
+        <v>72.75004211774282</v>
       </c>
       <c r="AH3" t="n">
-        <v>72.8645188724049</v>
+        <v>72.86451887240467</v>
       </c>
       <c r="AI3" t="n">
-        <v>72.97939150554525</v>
+        <v>72.97939150554549</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>0.75.3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.64813531277566</v>
+        <v>33.75932378572766</v>
       </c>
       <c r="C4" t="n">
-        <v>39.61503944944024</v>
+        <v>35.94835390634334</v>
       </c>
       <c r="D4" t="n">
-        <v>41.58038246311559</v>
+        <v>38.63627105762287</v>
       </c>
       <c r="E4" t="n">
-        <v>43.5448159177198</v>
+        <v>41.82304864640253</v>
       </c>
       <c r="F4" t="n">
-        <v>45.51058583439485</v>
+        <v>45.51058583439487</v>
       </c>
       <c r="G4" t="n">
         <v>47.48031490885189</v>
       </c>
       <c r="H4" t="n">
-        <v>49.45610450030064</v>
+        <v>49.45610450030065</v>
       </c>
       <c r="I4" t="n">
-        <v>51.4372137846154</v>
+        <v>51.43721378461541</v>
       </c>
       <c r="J4" t="n">
-        <v>53.42491402108867</v>
+        <v>53.42491402108869</v>
       </c>
       <c r="K4" t="n">
-        <v>55.37747231240391</v>
+        <v>55.37747231240393</v>
       </c>
       <c r="L4" t="n">
-        <v>57.28297242120528</v>
+        <v>57.28297242120531</v>
       </c>
       <c r="M4" t="n">
         <v>59.13452125226534</v>
       </c>
       <c r="N4" t="n">
-        <v>60.91284625467768</v>
+        <v>60.91284625467772</v>
       </c>
       <c r="O4" t="n">
-        <v>62.61899562523062</v>
+        <v>62.61899562523065</v>
       </c>
       <c r="P4" t="n">
-        <v>64.22501701821187</v>
+        <v>64.2250170182119</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.6631234538572</v>
+        <v>65.66312345385724</v>
       </c>
       <c r="R4" t="n">
-        <v>66.91463128533313</v>
+        <v>66.91463128533317</v>
       </c>
       <c r="S4" t="n">
-        <v>67.99900274669963</v>
+        <v>67.99900274669967</v>
       </c>
       <c r="T4" t="n">
-        <v>68.92959829222741</v>
+        <v>68.92959829222747</v>
       </c>
       <c r="U4" t="n">
-        <v>69.72685916567283</v>
+        <v>69.72685916567288</v>
       </c>
       <c r="V4" t="n">
-        <v>70.42267756602186</v>
+        <v>70.42267756602189</v>
       </c>
       <c r="W4" t="n">
-        <v>71.03741515998223</v>
+        <v>71.03741515998227</v>
       </c>
       <c r="X4" t="n">
         <v>71.54852152202054</v>
       </c>
       <c r="Y4" t="n">
-        <v>71.95269303670928</v>
+        <v>71.95269303670929</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.29520952546036</v>
+        <v>72.29520952546035</v>
       </c>
       <c r="AA4" t="n">
-        <v>72.60827505918972</v>
+        <v>72.60827505918971</v>
       </c>
       <c r="AB4" t="n">
-        <v>72.90597986903974</v>
+        <v>72.90597986903973</v>
       </c>
       <c r="AC4" t="n">
         <v>73.1807490913433</v>
       </c>
       <c r="AD4" t="n">
-        <v>73.44841560753947</v>
+        <v>73.44841560753946</v>
       </c>
       <c r="AE4" t="n">
         <v>73.71081456240228</v>
       </c>
       <c r="AF4" t="n">
-        <v>73.96999464671777</v>
+        <v>73.96999464671769</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.22748635768482</v>
+        <v>74.22748635768467</v>
       </c>
       <c r="AH4" t="n">
-        <v>74.48367020449112</v>
+        <v>74.48367020449128</v>
       </c>
       <c r="AI4" t="n">
-        <v>74.73843066462692</v>
+        <v>74.73843066462723</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>0.75.2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.66650973791776</v>
+        <v>31.21665197762</v>
       </c>
       <c r="C5" t="n">
-        <v>34.55904140458091</v>
+        <v>32.69988030741049</v>
       </c>
       <c r="D5" t="n">
-        <v>36.41465754861411</v>
+        <v>34.67074097965133</v>
       </c>
       <c r="E5" t="n">
-        <v>38.22653839640805</v>
+        <v>37.1082872266473</v>
       </c>
       <c r="F5" t="n">
-        <v>40.00573346625116</v>
+        <v>40.00573346625114</v>
       </c>
       <c r="G5" t="n">
-        <v>41.77082313568857</v>
+        <v>41.77082313568854</v>
       </c>
       <c r="H5" t="n">
-        <v>43.55164565638647</v>
+        <v>43.55164565638645</v>
       </c>
       <c r="I5" t="n">
         <v>45.42200089277724</v>
       </c>
       <c r="J5" t="n">
-        <v>47.13373311239199</v>
+        <v>47.13373311239202</v>
       </c>
       <c r="K5" t="n">
-        <v>48.71930824659918</v>
+        <v>48.71930824659917</v>
       </c>
       <c r="L5" t="n">
-        <v>50.12382826450248</v>
+        <v>50.12382826450249</v>
       </c>
       <c r="M5" t="n">
-        <v>51.6416881698401</v>
+        <v>51.64168816984007</v>
       </c>
       <c r="N5" t="n">
         <v>53.33154799260442</v>
       </c>
       <c r="O5" t="n">
-        <v>55.13472561165202</v>
+        <v>55.13472561165203</v>
       </c>
       <c r="P5" t="n">
         <v>57.01077318666517</v>
@@ -917,28 +905,28 @@
         <v>58.93729450552826</v>
       </c>
       <c r="R5" t="n">
-        <v>60.8873329883261</v>
+        <v>60.88733298832611</v>
       </c>
       <c r="S5" t="n">
-        <v>62.78690446694302</v>
+        <v>62.78690446694301</v>
       </c>
       <c r="T5" t="n">
-        <v>64.53300949079252</v>
+        <v>64.53300949079251</v>
       </c>
       <c r="U5" t="n">
-        <v>66.06883735241364</v>
+        <v>66.06883735241365</v>
       </c>
       <c r="V5" t="n">
-        <v>67.3928128084623</v>
+        <v>67.39281280846227</v>
       </c>
       <c r="W5" t="n">
         <v>68.52251154237564</v>
       </c>
       <c r="X5" t="n">
-        <v>69.4795064319855</v>
+        <v>69.47950643198547</v>
       </c>
       <c r="Y5" t="n">
-        <v>70.27908099221285</v>
+        <v>70.27908099221287</v>
       </c>
       <c r="Z5" t="n">
         <v>70.95285069773772</v>
@@ -950,56 +938,56 @@
         <v>72.01796252389198</v>
       </c>
       <c r="AC5" t="n">
-        <v>72.42536260060808</v>
+        <v>72.42536260060807</v>
       </c>
       <c r="AD5" t="n">
-        <v>72.82280900908076</v>
+        <v>72.82280900908077</v>
       </c>
       <c r="AE5" t="n">
-        <v>73.21953734553365</v>
+        <v>73.21953734553364</v>
       </c>
       <c r="AF5" t="n">
-        <v>73.61704007378296</v>
+        <v>73.617040073783</v>
       </c>
       <c r="AG5" t="n">
         <v>74.01567686416733</v>
       </c>
       <c r="AH5" t="n">
-        <v>74.4141460178536</v>
+        <v>74.41414601785375</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.81044282518779</v>
+        <v>74.81044282518778</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>0.75.1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.57534070848386</v>
+        <v>30.26023841260189</v>
       </c>
       <c r="C6" t="n">
-        <v>32.84755421035806</v>
+        <v>31.67789396891166</v>
       </c>
       <c r="D6" t="n">
-        <v>35.08517223917394</v>
+        <v>33.69265001374205</v>
       </c>
       <c r="E6" t="n">
-        <v>37.27178132309012</v>
+        <v>36.27612998281928</v>
       </c>
       <c r="F6" t="n">
-        <v>39.38898382657477</v>
+        <v>39.38898382657471</v>
       </c>
       <c r="G6" t="n">
         <v>41.44501763209787</v>
       </c>
       <c r="H6" t="n">
-        <v>43.47579111360299</v>
+        <v>43.47579111360291</v>
       </c>
       <c r="I6" t="n">
-        <v>45.57363319969863</v>
+        <v>45.57363319969857</v>
       </c>
       <c r="J6" t="n">
         <v>47.53252579321119</v>
@@ -1008,16 +996,16 @@
         <v>49.2584432472085</v>
       </c>
       <c r="L6" t="n">
-        <v>50.61196183610368</v>
+        <v>50.61196183610362</v>
       </c>
       <c r="M6" t="n">
-        <v>51.75855504245944</v>
+        <v>51.75855504245943</v>
       </c>
       <c r="N6" t="n">
-        <v>53.05092298153023</v>
+        <v>53.05092298153022</v>
       </c>
       <c r="O6" t="n">
-        <v>54.51668664565234</v>
+        <v>54.51668664565233</v>
       </c>
       <c r="P6" t="n">
         <v>56.11225233028835</v>
@@ -1029,7 +1017,7 @@
         <v>59.53970334868608</v>
       </c>
       <c r="S6" t="n">
-        <v>61.29485895652687</v>
+        <v>61.29485895652686</v>
       </c>
       <c r="T6" t="n">
         <v>63.00389990859497</v>
@@ -1038,65 +1026,65 @@
         <v>64.60643338969052</v>
       </c>
       <c r="V6" t="n">
-        <v>66.06233891647699</v>
+        <v>66.06233891647702</v>
       </c>
       <c r="W6" t="n">
         <v>67.35308036368625</v>
       </c>
       <c r="X6" t="n">
-        <v>68.46964618882495</v>
+        <v>68.46964618882497</v>
       </c>
       <c r="Y6" t="n">
         <v>69.41200860616539</v>
       </c>
       <c r="Z6" t="n">
-        <v>70.19630277135386</v>
+        <v>70.19630277135383</v>
       </c>
       <c r="AA6" t="n">
-        <v>70.84932761523582</v>
+        <v>70.84932761523584</v>
       </c>
       <c r="AB6" t="n">
-        <v>71.41237016376574</v>
+        <v>71.41237016376573</v>
       </c>
       <c r="AC6" t="n">
-        <v>71.88248076690388</v>
+        <v>71.8824807669039</v>
       </c>
       <c r="AD6" t="n">
-        <v>72.34546190298401</v>
+        <v>72.34546190298404</v>
       </c>
       <c r="AE6" t="n">
-        <v>72.80620351850958</v>
+        <v>72.80620351850961</v>
       </c>
       <c r="AF6" t="n">
-        <v>73.26442047352141</v>
+        <v>73.26442047352137</v>
       </c>
       <c r="AG6" t="n">
-        <v>73.71898877542162</v>
+        <v>73.71898877542155</v>
       </c>
       <c r="AH6" t="n">
-        <v>74.16834475963034</v>
+        <v>74.1683447596303</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.61167187357643</v>
+        <v>74.61167187357675</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.50053935762512</v>
+        <v>18.50053935762511</v>
       </c>
       <c r="C7" t="n">
-        <v>21.80862143487069</v>
+        <v>21.80862143487068</v>
       </c>
       <c r="D7" t="n">
         <v>25.12145729604289</v>
       </c>
       <c r="E7" t="n">
-        <v>28.4379073939785</v>
+        <v>28.43790739397849</v>
       </c>
       <c r="F7" t="n">
         <v>31.75449077420815</v>
@@ -1108,16 +1096,16 @@
         <v>38.349302678856</v>
       </c>
       <c r="I7" t="n">
-        <v>41.60983829746715</v>
+        <v>41.60983829746716</v>
       </c>
       <c r="J7" t="n">
-        <v>44.64749674166986</v>
+        <v>44.64749674166985</v>
       </c>
       <c r="K7" t="n">
-        <v>47.54708448131043</v>
+        <v>47.54708448131044</v>
       </c>
       <c r="L7" t="n">
-        <v>50.35661729570784</v>
+        <v>50.35661729570786</v>
       </c>
       <c r="M7" t="n">
         <v>53.06362382514062</v>
@@ -1126,10 +1114,10 @@
         <v>55.60790451950516</v>
       </c>
       <c r="O7" t="n">
-        <v>57.95984291589372</v>
+        <v>57.95984291589374</v>
       </c>
       <c r="P7" t="n">
-        <v>60.05695514634977</v>
+        <v>60.05695514634976</v>
       </c>
       <c r="Q7" t="n">
         <v>61.84564359560844</v>
@@ -1138,10 +1126,10 @@
         <v>63.3632198979555</v>
       </c>
       <c r="S7" t="n">
-        <v>64.69989213398235</v>
+        <v>64.69989213398233</v>
       </c>
       <c r="T7" t="n">
-        <v>65.90064958912714</v>
+        <v>65.90064958912718</v>
       </c>
       <c r="U7" t="n">
         <v>66.98229368325309</v>
@@ -1150,107 +1138,107 @@
         <v>67.94025631673301</v>
       </c>
       <c r="W7" t="n">
-        <v>68.75876916454555</v>
+        <v>68.75876916454554</v>
       </c>
       <c r="X7" t="n">
-        <v>69.4377635122367</v>
+        <v>69.43776351223669</v>
       </c>
       <c r="Y7" t="n">
         <v>69.99506700131417</v>
       </c>
       <c r="Z7" t="n">
-        <v>70.46500657197228</v>
+        <v>70.4650065719723</v>
       </c>
       <c r="AA7" t="n">
         <v>70.86759145376142</v>
       </c>
       <c r="AB7" t="n">
-        <v>71.21234798630061</v>
+        <v>71.21234798630063</v>
       </c>
       <c r="AC7" t="n">
         <v>71.45815006378729</v>
       </c>
       <c r="AD7" t="n">
-        <v>71.69620992999907</v>
+        <v>71.69620992999909</v>
       </c>
       <c r="AE7" t="n">
-        <v>71.92929264152853</v>
+        <v>71.92929264152856</v>
       </c>
       <c r="AF7" t="n">
-        <v>72.15731423142034</v>
+        <v>72.15731423142024</v>
       </c>
       <c r="AG7" t="n">
-        <v>72.38024680347861</v>
+        <v>72.38024680347857</v>
       </c>
       <c r="AH7" t="n">
-        <v>72.59769745632229</v>
+        <v>72.59769745632232</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.80920004223846</v>
+        <v>72.80920004223849</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>0.375.3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.83603666376094</v>
+        <v>35.9180183318805</v>
       </c>
       <c r="C8" t="n">
-        <v>43.08899493203351</v>
+        <v>38.18062183252083</v>
       </c>
       <c r="D8" t="n">
-        <v>44.33911571734017</v>
+        <v>40.75433678800506</v>
       </c>
       <c r="E8" t="n">
-        <v>45.58644254908398</v>
+        <v>43.63813723044846</v>
       </c>
       <c r="F8" t="n">
-        <v>46.83208012207515</v>
+        <v>46.83208012207513</v>
       </c>
       <c r="G8" t="n">
         <v>48.08041888701156</v>
       </c>
       <c r="H8" t="n">
-        <v>49.33583144619779</v>
+        <v>49.33583144619778</v>
       </c>
       <c r="I8" t="n">
-        <v>50.5987894540042</v>
+        <v>50.59878945400416</v>
       </c>
       <c r="J8" t="n">
-        <v>51.86846652960913</v>
+        <v>51.86846652960912</v>
       </c>
       <c r="K8" t="n">
         <v>53.14141732138538</v>
       </c>
       <c r="L8" t="n">
-        <v>54.41640030418261</v>
+        <v>54.41640030418259</v>
       </c>
       <c r="M8" t="n">
-        <v>55.70675973871111</v>
+        <v>55.70675973871109</v>
       </c>
       <c r="N8" t="n">
-        <v>57.03091668743722</v>
+        <v>57.03091668743721</v>
       </c>
       <c r="O8" t="n">
         <v>58.38193377326576</v>
       </c>
       <c r="P8" t="n">
-        <v>59.73908041874709</v>
+        <v>59.7390804187471</v>
       </c>
       <c r="Q8" t="n">
         <v>61.07356203885817</v>
       </c>
       <c r="R8" t="n">
-        <v>62.36641825198715</v>
+        <v>62.36641825198714</v>
       </c>
       <c r="S8" t="n">
         <v>63.60789604771622</v>
       </c>
       <c r="T8" t="n">
-        <v>64.79795013725759</v>
+        <v>64.79795013725757</v>
       </c>
       <c r="U8" t="n">
         <v>65.9266978565395</v>
@@ -1259,74 +1247,74 @@
         <v>66.98241989498385</v>
       </c>
       <c r="W8" t="n">
-        <v>67.94486716071805</v>
+        <v>67.94486716071803</v>
       </c>
       <c r="X8" t="n">
         <v>68.80550534149411</v>
       </c>
       <c r="Y8" t="n">
-        <v>69.56609746262367</v>
+        <v>69.56609746262365</v>
       </c>
       <c r="Z8" t="n">
-        <v>70.23542724271083</v>
+        <v>70.23542724271084</v>
       </c>
       <c r="AA8" t="n">
         <v>70.83974043914375</v>
       </c>
       <c r="AB8" t="n">
-        <v>71.39272798260738</v>
+        <v>71.39272798260737</v>
       </c>
       <c r="AC8" t="n">
         <v>71.86339623512002</v>
       </c>
       <c r="AD8" t="n">
-        <v>72.32621598303349</v>
+        <v>72.32621598303351</v>
       </c>
       <c r="AE8" t="n">
         <v>72.78311314446114</v>
       </c>
       <c r="AF8" t="n">
-        <v>73.23480348823786</v>
+        <v>73.23480348823793</v>
       </c>
       <c r="AG8" t="n">
-        <v>73.68219401889843</v>
+        <v>73.68219401889841</v>
       </c>
       <c r="AH8" t="n">
-        <v>74.12584116657219</v>
+        <v>74.12584116657213</v>
       </c>
       <c r="AI8" t="n">
-        <v>74.56580012389549</v>
+        <v>74.56580012389551</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>0.375</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.10789118567124</v>
+        <v>31.90087690266724</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83632082909931</v>
+        <v>33.48459529990101</v>
       </c>
       <c r="D9" t="n">
-        <v>37.56314622038659</v>
+        <v>35.53145027490185</v>
       </c>
       <c r="E9" t="n">
-        <v>39.28882915136436</v>
+        <v>38.04119516577141</v>
       </c>
       <c r="F9" t="n">
-        <v>41.01520650157246</v>
+        <v>41.01520650157249</v>
       </c>
       <c r="G9" t="n">
-        <v>42.7477377023769</v>
+        <v>42.74773770237694</v>
       </c>
       <c r="H9" t="n">
-        <v>44.48989215828922</v>
+        <v>44.48989215828926</v>
       </c>
       <c r="I9" t="n">
-        <v>46.23955024718531</v>
+        <v>46.23955024718533</v>
       </c>
       <c r="J9" t="n">
         <v>47.9952664785636</v>
@@ -1335,13 +1323,13 @@
         <v>49.74593648704396</v>
       </c>
       <c r="L9" t="n">
-        <v>51.48601476762668</v>
+        <v>51.48601476762669</v>
       </c>
       <c r="M9" t="n">
         <v>53.2107873055476</v>
       </c>
       <c r="N9" t="n">
-        <v>54.90608221063924</v>
+        <v>54.90608221063923</v>
       </c>
       <c r="O9" t="n">
         <v>56.54054209973822</v>
@@ -1350,16 +1338,16 @@
         <v>58.08510300553429</v>
       </c>
       <c r="Q9" t="n">
-        <v>59.52842198626858</v>
+        <v>59.52842198626859</v>
       </c>
       <c r="R9" t="n">
-        <v>60.87366970851453</v>
+        <v>60.87366970851455</v>
       </c>
       <c r="S9" t="n">
-        <v>62.11749952096526</v>
+        <v>62.11749952096528</v>
       </c>
       <c r="T9" t="n">
-        <v>63.25547187066384</v>
+        <v>63.25547187066383</v>
       </c>
       <c r="U9" t="n">
         <v>64.28295310173125</v>
@@ -1374,83 +1362,83 @@
         <v>66.64519566934638</v>
       </c>
       <c r="Y9" t="n">
-        <v>67.22796613337221</v>
+        <v>67.22796613337223</v>
       </c>
       <c r="Z9" t="n">
         <v>67.73694974090733</v>
       </c>
       <c r="AA9" t="n">
-        <v>68.18119517020983</v>
+        <v>68.18119517020982</v>
       </c>
       <c r="AB9" t="n">
-        <v>68.56719807120136</v>
+        <v>68.56719807120137</v>
       </c>
       <c r="AC9" t="n">
-        <v>68.84725712082113</v>
+        <v>68.84725712082111</v>
       </c>
       <c r="AD9" t="n">
-        <v>69.11722098892173</v>
+        <v>69.11722098892172</v>
       </c>
       <c r="AE9" t="n">
         <v>69.38061391232547</v>
       </c>
       <c r="AF9" t="n">
-        <v>69.63775561681828</v>
+        <v>69.63775561681834</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.88869457620943</v>
+        <v>69.88869457620955</v>
       </c>
       <c r="AH9" t="n">
-        <v>70.13337778503774</v>
+        <v>70.13337778503767</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.3718213583097</v>
+        <v>70.37182135830973</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>0.375.2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.90036830786278</v>
+        <v>32.75390696912593</v>
       </c>
       <c r="C10" t="n">
-        <v>37.34271012505102</v>
+        <v>34.406001051411</v>
       </c>
       <c r="D10" t="n">
-        <v>38.77991459647127</v>
+        <v>36.43890295162237</v>
       </c>
       <c r="E10" t="n">
-        <v>40.21170832245407</v>
+        <v>38.85032104277182</v>
       </c>
       <c r="F10" t="n">
-        <v>41.63914505693382</v>
+        <v>41.6391450569338</v>
       </c>
       <c r="G10" t="n">
-        <v>43.06766022579349</v>
+        <v>43.06766022579347</v>
       </c>
       <c r="H10" t="n">
         <v>44.50362066636767</v>
       </c>
       <c r="I10" t="n">
-        <v>45.95010200204637</v>
+        <v>45.95010200204636</v>
       </c>
       <c r="J10" t="n">
-        <v>47.43318087524672</v>
+        <v>47.4331808752467</v>
       </c>
       <c r="K10" t="n">
-        <v>48.94256459516669</v>
+        <v>48.94256459516667</v>
       </c>
       <c r="L10" t="n">
-        <v>50.46912352618111</v>
+        <v>50.46912352618113</v>
       </c>
       <c r="M10" t="n">
         <v>52.0173249608942</v>
       </c>
       <c r="N10" t="n">
-        <v>53.60556175160263</v>
+        <v>53.60556175160261</v>
       </c>
       <c r="O10" t="n">
         <v>55.23510644949587</v>
@@ -1459,128 +1447,128 @@
         <v>56.88241804338649</v>
       </c>
       <c r="Q10" t="n">
-        <v>58.50805581534689</v>
+        <v>58.5080558153469</v>
       </c>
       <c r="R10" t="n">
-        <v>60.06449631911686</v>
+        <v>60.06449631911687</v>
       </c>
       <c r="S10" t="n">
-        <v>61.52124650559308</v>
+        <v>61.52124650559306</v>
       </c>
       <c r="T10" t="n">
-        <v>62.87650764768361</v>
+        <v>62.87650764768362</v>
       </c>
       <c r="U10" t="n">
-        <v>64.13113557454909</v>
+        <v>64.13113557454911</v>
       </c>
       <c r="V10" t="n">
-        <v>65.27064901062795</v>
+        <v>65.27064901062796</v>
       </c>
       <c r="W10" t="n">
-        <v>66.27114947603218</v>
+        <v>66.27114947603219</v>
       </c>
       <c r="X10" t="n">
-        <v>67.12021494341906</v>
+        <v>67.12021494341907</v>
       </c>
       <c r="Y10" t="n">
         <v>67.82397851109178</v>
       </c>
       <c r="Z10" t="n">
-        <v>68.40737610078622</v>
+        <v>68.40737610078621</v>
       </c>
       <c r="AA10" t="n">
-        <v>68.89250754601899</v>
+        <v>68.892507546019</v>
       </c>
       <c r="AB10" t="n">
-        <v>69.29610599662993</v>
+        <v>69.29610599662995</v>
       </c>
       <c r="AC10" t="n">
-        <v>69.56671958072155</v>
+        <v>69.56671958072154</v>
       </c>
       <c r="AD10" t="n">
-        <v>69.81821550179637</v>
+        <v>69.81821550179636</v>
       </c>
       <c r="AE10" t="n">
-        <v>70.0600405453411</v>
+        <v>70.06004054534111</v>
       </c>
       <c r="AF10" t="n">
-        <v>70.29520378873325</v>
+        <v>70.29520378873323</v>
       </c>
       <c r="AG10" t="n">
-        <v>70.52502966346989</v>
+        <v>70.52502966346994</v>
       </c>
       <c r="AH10" t="n">
-        <v>70.74888905534185</v>
+        <v>70.74888905534192</v>
       </c>
       <c r="AI10" t="n">
-        <v>70.96559106236688</v>
+        <v>70.96559106236694</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>0.1875.2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.35843440242706</v>
+        <v>28.35843440242689</v>
       </c>
       <c r="C11" t="n">
-        <v>31.89575467648899</v>
+        <v>31.13853727962591</v>
       </c>
       <c r="D11" t="n">
-        <v>35.30726050103431</v>
+        <v>33.89401505990649</v>
       </c>
       <c r="E11" t="n">
-        <v>38.58975882296</v>
+        <v>37.44609558139025</v>
       </c>
       <c r="F11" t="n">
-        <v>41.74758442418801</v>
+        <v>41.74758442418796</v>
       </c>
       <c r="G11" t="n">
-        <v>44.78799439288354</v>
+        <v>44.78799439288351</v>
       </c>
       <c r="H11" t="n">
-        <v>47.72291666442519</v>
+        <v>47.72291666442518</v>
       </c>
       <c r="I11" t="n">
-        <v>50.58569020848846</v>
+        <v>50.58569020848847</v>
       </c>
       <c r="J11" t="n">
-        <v>52.63092592091598</v>
+        <v>52.63092592091601</v>
       </c>
       <c r="K11" t="n">
-        <v>54.678805505897</v>
+        <v>54.67880550589702</v>
       </c>
       <c r="L11" t="n">
-        <v>56.62249038382824</v>
+        <v>56.62249038382827</v>
       </c>
       <c r="M11" t="n">
-        <v>58.31151144183949</v>
+        <v>58.31151144183946</v>
       </c>
       <c r="N11" t="n">
-        <v>59.60853882614043</v>
+        <v>59.60853882614039</v>
       </c>
       <c r="O11" t="n">
-        <v>60.53632244354394</v>
+        <v>60.53632244354391</v>
       </c>
       <c r="P11" t="n">
-        <v>61.35358546358759</v>
+        <v>61.35358546358757</v>
       </c>
       <c r="Q11" t="n">
         <v>62.28119672082608</v>
       </c>
       <c r="R11" t="n">
-        <v>63.30505541534839</v>
+        <v>63.3050554153484</v>
       </c>
       <c r="S11" t="n">
-        <v>64.37274080961791</v>
+        <v>64.37274080961789</v>
       </c>
       <c r="T11" t="n">
-        <v>65.46679211936348</v>
+        <v>65.4667921193635</v>
       </c>
       <c r="U11" t="n">
-        <v>66.5957813478324</v>
+        <v>66.59578134783239</v>
       </c>
       <c r="V11" t="n">
         <v>67.73101823699116</v>
@@ -1589,53 +1577,53 @@
         <v>68.80449737497962</v>
       </c>
       <c r="X11" t="n">
-        <v>69.77304451628899</v>
+        <v>69.77304451628898</v>
       </c>
       <c r="Y11" t="n">
-        <v>70.62220621864289</v>
+        <v>70.6222062186429</v>
       </c>
       <c r="Z11" t="n">
-        <v>71.36132051551652</v>
+        <v>71.36132051551651</v>
       </c>
       <c r="AA11" t="n">
         <v>72.01007815835484</v>
       </c>
       <c r="AB11" t="n">
-        <v>72.57911628543265</v>
+        <v>72.57911628543263</v>
       </c>
       <c r="AC11" t="n">
         <v>73.04264325568602</v>
       </c>
       <c r="AD11" t="n">
-        <v>73.49590408034103</v>
+        <v>73.49590408034102</v>
       </c>
       <c r="AE11" t="n">
         <v>73.94441700100778</v>
       </c>
       <c r="AF11" t="n">
-        <v>74.38921462062704</v>
+        <v>74.38921462062697</v>
       </c>
       <c r="AG11" t="n">
-        <v>74.83024402818836</v>
+        <v>74.83024402818822</v>
       </c>
       <c r="AH11" t="n">
-        <v>75.26640833821443</v>
+        <v>75.26640833821442</v>
       </c>
       <c r="AI11" t="n">
-        <v>75.69645249948641</v>
+        <v>75.69645249948618</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>0.1875.1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.23259610866715</v>
+        <v>17.23259610866712</v>
       </c>
       <c r="C12" t="n">
-        <v>21.13082231112966</v>
+        <v>21.13082231112967</v>
       </c>
       <c r="D12" t="n">
         <v>25.06760220541353</v>
@@ -1659,83 +1647,83 @@
         <v>48.20719598444781</v>
       </c>
       <c r="K12" t="n">
-        <v>51.31085059195242</v>
+        <v>51.3108505919524</v>
       </c>
       <c r="L12" t="n">
         <v>53.89416366663868</v>
       </c>
       <c r="M12" t="n">
-        <v>55.96469384370857</v>
+        <v>55.96469384370855</v>
       </c>
       <c r="N12" t="n">
-        <v>57.49019588233671</v>
+        <v>57.49019588233672</v>
       </c>
       <c r="O12" t="n">
-        <v>58.43865802228908</v>
+        <v>58.4386580222891</v>
       </c>
       <c r="P12" t="n">
-        <v>58.99210447825715</v>
+        <v>58.99210447825713</v>
       </c>
       <c r="Q12" t="n">
-        <v>59.48172840966706</v>
+        <v>59.48172840966705</v>
       </c>
       <c r="R12" t="n">
-        <v>60.04633412895836</v>
+        <v>60.04633412895834</v>
       </c>
       <c r="S12" t="n">
-        <v>60.72679227023454</v>
+        <v>60.72679227023453</v>
       </c>
       <c r="T12" t="n">
-        <v>61.59114199376938</v>
+        <v>61.59114199376939</v>
       </c>
       <c r="U12" t="n">
-        <v>62.68691628637902</v>
+        <v>62.68691628637905</v>
       </c>
       <c r="V12" t="n">
         <v>63.99427504602347</v>
       </c>
       <c r="W12" t="n">
-        <v>65.44230776242206</v>
+        <v>65.44230776242205</v>
       </c>
       <c r="X12" t="n">
-        <v>66.93456198187478</v>
+        <v>66.93456198187477</v>
       </c>
       <c r="Y12" t="n">
-        <v>68.34371218676972</v>
+        <v>68.34371218676975</v>
       </c>
       <c r="Z12" t="n">
-        <v>69.58587383216246</v>
+        <v>69.58587383216245</v>
       </c>
       <c r="AA12" t="n">
-        <v>70.6350762727558</v>
+        <v>70.63507627275575</v>
       </c>
       <c r="AB12" t="n">
-        <v>71.49349504892443</v>
+        <v>71.49349504892444</v>
       </c>
       <c r="AC12" t="n">
-        <v>72.07414045470239</v>
+        <v>72.07414045470242</v>
       </c>
       <c r="AD12" t="n">
-        <v>72.6320531331944</v>
+        <v>72.63205313319442</v>
       </c>
       <c r="AE12" t="n">
-        <v>73.17298775788646</v>
+        <v>73.17298775788645</v>
       </c>
       <c r="AF12" t="n">
-        <v>73.69916329929953</v>
+        <v>73.69916329929943</v>
       </c>
       <c r="AG12" t="n">
-        <v>74.21307075004019</v>
+        <v>74.21307075004023</v>
       </c>
       <c r="AH12" t="n">
-        <v>74.71569522124878</v>
+        <v>74.71569522124864</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.2069225819526</v>
+        <v>75.20692258195243</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.1875</t>
         </is>
@@ -1744,22 +1732,22 @@
         <v>14.78154064167992</v>
       </c>
       <c r="C13" t="n">
-        <v>18.49114039739523</v>
+        <v>18.49114039739522</v>
       </c>
       <c r="D13" t="n">
         <v>22.15592045618211</v>
       </c>
       <c r="E13" t="n">
-        <v>25.77865443091821</v>
+        <v>25.7786544309182</v>
       </c>
       <c r="F13" t="n">
         <v>29.36809026780547</v>
       </c>
       <c r="G13" t="n">
-        <v>32.93635319607739</v>
+        <v>32.9363531960774</v>
       </c>
       <c r="H13" t="n">
-        <v>36.50196502981427</v>
+        <v>36.50196502981426</v>
       </c>
       <c r="I13" t="n">
         <v>40.12883217700082</v>
@@ -1768,25 +1756,25 @@
         <v>43.30052263614685</v>
       </c>
       <c r="K13" t="n">
-        <v>46.66954800813154</v>
+        <v>46.66954800813153</v>
       </c>
       <c r="L13" t="n">
-        <v>50.72740810531625</v>
+        <v>50.72740810531624</v>
       </c>
       <c r="M13" t="n">
         <v>54.46097078654578</v>
       </c>
       <c r="N13" t="n">
-        <v>55.79502372504383</v>
+        <v>55.79502372504385</v>
       </c>
       <c r="O13" t="n">
-        <v>56.50350204754829</v>
+        <v>56.50350204754827</v>
       </c>
       <c r="P13" t="n">
-        <v>57.26426218433544</v>
+        <v>57.26426218433541</v>
       </c>
       <c r="Q13" t="n">
-        <v>58.11771378752339</v>
+        <v>58.1177137875234</v>
       </c>
       <c r="R13" t="n">
         <v>59.0491486012615</v>
@@ -1804,13 +1792,13 @@
         <v>63.35651522219484</v>
       </c>
       <c r="W13" t="n">
-        <v>64.58621469174484</v>
+        <v>64.58621469174483</v>
       </c>
       <c r="X13" t="n">
-        <v>65.82712914250195</v>
+        <v>65.82712914250193</v>
       </c>
       <c r="Y13" t="n">
-        <v>67.02883258298125</v>
+        <v>67.02883258298122</v>
       </c>
       <c r="Z13" t="n">
         <v>68.16025063958661</v>
@@ -1819,98 +1807,98 @@
         <v>69.21427156325326</v>
       </c>
       <c r="AB13" t="n">
-        <v>70.18707171796093</v>
+        <v>70.1870717179609</v>
       </c>
       <c r="AC13" t="n">
-        <v>70.96136910312421</v>
+        <v>70.96136910312423</v>
       </c>
       <c r="AD13" t="n">
-        <v>71.71069554078036</v>
+        <v>71.71069554078035</v>
       </c>
       <c r="AE13" t="n">
-        <v>72.4451455603166</v>
+        <v>72.44514556031658</v>
       </c>
       <c r="AF13" t="n">
-        <v>73.16468015719119</v>
+        <v>73.16468015719113</v>
       </c>
       <c r="AG13" t="n">
-        <v>73.86906552988029</v>
+        <v>73.86906552988027</v>
       </c>
       <c r="AH13" t="n">
-        <v>74.55714596559059</v>
+        <v>74.55714596559069</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.22714662946298</v>
+        <v>75.22714662946291</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.0938</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.3605420582834</v>
+        <v>32.06497410921713</v>
       </c>
       <c r="C14" t="n">
-        <v>36.50347806702873</v>
+        <v>33.93570513732495</v>
       </c>
       <c r="D14" t="n">
-        <v>38.61204896228053</v>
+        <v>36.3451812988846</v>
       </c>
       <c r="E14" t="n">
-        <v>40.67923502034564</v>
+        <v>39.27373833520974</v>
       </c>
       <c r="F14" t="n">
-        <v>42.70446286748956</v>
+        <v>42.70446286748952</v>
       </c>
       <c r="G14" t="n">
-        <v>44.69307658670763</v>
+        <v>44.69307658670761</v>
       </c>
       <c r="H14" t="n">
-        <v>46.65063697626104</v>
+        <v>46.65063697626102</v>
       </c>
       <c r="I14" t="n">
         <v>48.57917450622627</v>
       </c>
       <c r="J14" t="n">
-        <v>50.21441509980945</v>
+        <v>50.21441509980944</v>
       </c>
       <c r="K14" t="n">
-        <v>51.67071049021973</v>
+        <v>51.67071049021975</v>
       </c>
       <c r="L14" t="n">
         <v>52.94577596144548</v>
       </c>
       <c r="M14" t="n">
-        <v>54.05400827895884</v>
+        <v>54.05400827895883</v>
       </c>
       <c r="N14" t="n">
-        <v>55.02509740646339</v>
+        <v>55.0250974064634</v>
       </c>
       <c r="O14" t="n">
-        <v>55.89076846373172</v>
+        <v>55.89076846373175</v>
       </c>
       <c r="P14" t="n">
         <v>56.69101639615125</v>
       </c>
       <c r="Q14" t="n">
-        <v>57.47753089606508</v>
+        <v>57.47753089606509</v>
       </c>
       <c r="R14" t="n">
-        <v>58.29943791044567</v>
+        <v>58.29943791044568</v>
       </c>
       <c r="S14" t="n">
-        <v>59.2001511541242</v>
+        <v>59.20015115412419</v>
       </c>
       <c r="T14" t="n">
-        <v>60.20296822699818</v>
+        <v>60.20296822699816</v>
       </c>
       <c r="U14" t="n">
         <v>61.30220614117729</v>
       </c>
       <c r="V14" t="n">
-        <v>62.46821163760873</v>
+        <v>62.46821163760874</v>
       </c>
       <c r="W14" t="n">
         <v>63.67381549932963</v>
@@ -1922,44 +1910,44 @@
         <v>66.09193865992623</v>
       </c>
       <c r="Z14" t="n">
-        <v>67.25343150623273</v>
+        <v>67.25343150623274</v>
       </c>
       <c r="AA14" t="n">
-        <v>68.35591233953598</v>
+        <v>68.35591233953596</v>
       </c>
       <c r="AB14" t="n">
-        <v>69.35933564177907</v>
+        <v>69.35933564177905</v>
       </c>
       <c r="AC14" t="n">
-        <v>70.12109648352489</v>
+        <v>70.12109648352488</v>
       </c>
       <c r="AD14" t="n">
-        <v>70.85998015966894</v>
+        <v>70.85998015966892</v>
       </c>
       <c r="AE14" t="n">
         <v>71.58652139009253</v>
       </c>
       <c r="AF14" t="n">
-        <v>72.30020531165698</v>
+        <v>72.30020531165688</v>
       </c>
       <c r="AG14" t="n">
-        <v>72.99974814379173</v>
+        <v>72.99974814379162</v>
       </c>
       <c r="AH14" t="n">
         <v>73.68324307227407</v>
       </c>
       <c r="AI14" t="n">
-        <v>74.34897821156959</v>
+        <v>74.34897821156962</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.0938.2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.99772645962465</v>
+        <v>18.99772645962463</v>
       </c>
       <c r="C15" t="n">
         <v>22.16075447502326</v>
@@ -1968,7 +1956,7 @@
         <v>25.31188806028012</v>
       </c>
       <c r="E15" t="n">
-        <v>28.43929679523092</v>
+        <v>28.43929679523093</v>
       </c>
       <c r="F15" t="n">
         <v>31.53149129999072</v>
@@ -1983,37 +1971,37 @@
         <v>40.73594593974308</v>
       </c>
       <c r="J15" t="n">
-        <v>43.52811214078385</v>
+        <v>43.52811214078383</v>
       </c>
       <c r="K15" t="n">
         <v>45.86378771238783</v>
       </c>
       <c r="L15" t="n">
-        <v>47.862677265814</v>
+        <v>47.86267726581401</v>
       </c>
       <c r="M15" t="n">
         <v>49.5816225896122</v>
       </c>
       <c r="N15" t="n">
-        <v>50.93663428783667</v>
+        <v>50.93663428783666</v>
       </c>
       <c r="O15" t="n">
-        <v>51.88451673895991</v>
+        <v>51.8845167389599</v>
       </c>
       <c r="P15" t="n">
         <v>52.55057684992979</v>
       </c>
       <c r="Q15" t="n">
-        <v>53.08197196608607</v>
+        <v>53.08197196608608</v>
       </c>
       <c r="R15" t="n">
         <v>53.59618993387838</v>
       </c>
       <c r="S15" t="n">
-        <v>54.19947973562946</v>
+        <v>54.19947973562948</v>
       </c>
       <c r="T15" t="n">
-        <v>54.95067014164317</v>
+        <v>54.95067014164316</v>
       </c>
       <c r="U15" t="n">
         <v>55.86282557303865</v>
@@ -2022,16 +2010,16 @@
         <v>56.92920517402496</v>
       </c>
       <c r="W15" t="n">
-        <v>58.13945556029724</v>
+        <v>58.13945556029725</v>
       </c>
       <c r="X15" t="n">
-        <v>59.47688327156617</v>
+        <v>59.47688327156618</v>
       </c>
       <c r="Y15" t="n">
-        <v>60.92114411135458</v>
+        <v>60.92114411135456</v>
       </c>
       <c r="Z15" t="n">
-        <v>62.43718545419833</v>
+        <v>62.43718545419835</v>
       </c>
       <c r="AA15" t="n">
         <v>63.9593931693141</v>
@@ -2046,77 +2034,77 @@
         <v>67.45482555439851</v>
       </c>
       <c r="AE15" t="n">
-        <v>68.44081433389887</v>
+        <v>68.44081433389893</v>
       </c>
       <c r="AF15" t="n">
-        <v>69.39561659174144</v>
+        <v>69.39561659174142</v>
       </c>
       <c r="AG15" t="n">
-        <v>70.31637883500639</v>
+        <v>70.31637883500647</v>
       </c>
       <c r="AH15" t="n">
-        <v>71.20091776381132</v>
+        <v>71.20091776381126</v>
       </c>
       <c r="AI15" t="n">
-        <v>72.0483826205614</v>
+        <v>72.04838262056163</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>0.0938.1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.801768075448629</v>
+        <v>-2.801768075448607</v>
       </c>
       <c r="C16" t="n">
-        <v>1.640192878771515</v>
+        <v>1.640192878771532</v>
       </c>
       <c r="D16" t="n">
-        <v>6.071154612932624</v>
+        <v>6.071154612932641</v>
       </c>
       <c r="E16" t="n">
         <v>10.48308630307286</v>
       </c>
       <c r="F16" t="n">
-        <v>14.86279099508496</v>
+        <v>14.86279099508495</v>
       </c>
       <c r="G16" t="n">
-        <v>19.20146559839586</v>
+        <v>19.20146559839585</v>
       </c>
       <c r="H16" t="n">
-        <v>23.49795065287124</v>
+        <v>23.49795065287122</v>
       </c>
       <c r="I16" t="n">
-        <v>27.7674293500866</v>
+        <v>27.76742935008658</v>
       </c>
       <c r="J16" t="n">
-        <v>31.43740835438447</v>
+        <v>31.43740835438443</v>
       </c>
       <c r="K16" t="n">
-        <v>35.01306446440737</v>
+        <v>35.01306446440734</v>
       </c>
       <c r="L16" t="n">
-        <v>38.54204992828571</v>
+        <v>38.54204992828566</v>
       </c>
       <c r="M16" t="n">
-        <v>42.04104055112089</v>
+        <v>42.04104055112091</v>
       </c>
       <c r="N16" t="n">
-        <v>45.73447385094561</v>
+        <v>45.73447385094557</v>
       </c>
       <c r="O16" t="n">
-        <v>48.56513821212665</v>
+        <v>48.56513821212661</v>
       </c>
       <c r="P16" t="n">
-        <v>49.71646342208</v>
+        <v>49.71646342208001</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.6534572222568</v>
+        <v>50.65345722225681</v>
       </c>
       <c r="R16" t="n">
-        <v>51.78501336177571</v>
+        <v>51.7850133617757</v>
       </c>
       <c r="S16" t="n">
         <v>53.07317198935371</v>
@@ -2125,65 +2113,65 @@
         <v>54.45184346795462</v>
       </c>
       <c r="U16" t="n">
-        <v>55.86969731864758</v>
+        <v>55.86969731864759</v>
       </c>
       <c r="V16" t="n">
-        <v>57.31056276526528</v>
+        <v>57.31056276526527</v>
       </c>
       <c r="W16" t="n">
-        <v>58.75708773373591</v>
+        <v>58.75708773373592</v>
       </c>
       <c r="X16" t="n">
         <v>60.1800218556268</v>
       </c>
       <c r="Y16" t="n">
-        <v>61.54225912730099</v>
+        <v>61.54225912730098</v>
       </c>
       <c r="Z16" t="n">
         <v>62.79851160092448</v>
       </c>
       <c r="AA16" t="n">
-        <v>63.89950420690437</v>
+        <v>63.89950420690436</v>
       </c>
       <c r="AB16" t="n">
-        <v>64.82217017891294</v>
+        <v>64.82217017891296</v>
       </c>
       <c r="AC16" t="n">
-        <v>65.47433997019098</v>
+        <v>65.47433997019095</v>
       </c>
       <c r="AD16" t="n">
-        <v>66.10502405431144</v>
+        <v>66.10502405431143</v>
       </c>
       <c r="AE16" t="n">
-        <v>66.72288222754544</v>
+        <v>66.72288222754541</v>
       </c>
       <c r="AF16" t="n">
-        <v>67.32921333705775</v>
+        <v>67.32921333705778</v>
       </c>
       <c r="AG16" t="n">
-        <v>67.92413493188346</v>
+        <v>67.92413493188347</v>
       </c>
       <c r="AH16" t="n">
-        <v>68.50652446312156</v>
+        <v>68.50652446312166</v>
       </c>
       <c r="AI16" t="n">
-        <v>69.07523517527396</v>
+        <v>69.07523517527397</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>0.0469.2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.330950637534355</v>
+        <v>6.330950637534356</v>
       </c>
       <c r="C17" t="n">
-        <v>10.02577437691609</v>
+        <v>10.0257743769161</v>
       </c>
       <c r="D17" t="n">
-        <v>13.70762024647899</v>
+        <v>13.707620246479</v>
       </c>
       <c r="E17" t="n">
         <v>17.36470822576764</v>
@@ -2198,22 +2186,22 @@
         <v>28.14896294120075</v>
       </c>
       <c r="I17" t="n">
-        <v>31.74799408509895</v>
+        <v>31.74799408509896</v>
       </c>
       <c r="J17" t="n">
-        <v>34.97900603990645</v>
+        <v>34.97900603990646</v>
       </c>
       <c r="K17" t="n">
         <v>37.98948090650219</v>
       </c>
       <c r="L17" t="n">
-        <v>40.76009012810341</v>
+        <v>40.76009012810343</v>
       </c>
       <c r="M17" t="n">
         <v>43.32659672000339</v>
       </c>
       <c r="N17" t="n">
-        <v>45.70114283767144</v>
+        <v>45.70114283767143</v>
       </c>
       <c r="O17" t="n">
         <v>47.88130030282655</v>
@@ -2222,71 +2210,71 @@
         <v>49.89550155546481</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.77163142627258</v>
+        <v>51.77163142627257</v>
       </c>
       <c r="R17" t="n">
-        <v>53.5572662452942</v>
+        <v>53.55726624529419</v>
       </c>
       <c r="S17" t="n">
         <v>55.26598448178157</v>
       </c>
       <c r="T17" t="n">
-        <v>56.90504293403151</v>
+        <v>56.90504293403153</v>
       </c>
       <c r="U17" t="n">
-        <v>58.46455033942314</v>
+        <v>58.46455033942315</v>
       </c>
       <c r="V17" t="n">
-        <v>59.92071932433365</v>
+        <v>59.92071932433364</v>
       </c>
       <c r="W17" t="n">
-        <v>61.24344559450524</v>
+        <v>61.24344559450525</v>
       </c>
       <c r="X17" t="n">
-        <v>62.44637918002001</v>
+        <v>62.44637918002</v>
       </c>
       <c r="Y17" t="n">
         <v>63.61378012253729</v>
       </c>
       <c r="Z17" t="n">
-        <v>64.86283734131224</v>
+        <v>64.86283734131226</v>
       </c>
       <c r="AA17" t="n">
-        <v>66.25622220696869</v>
+        <v>66.2562222069687</v>
       </c>
       <c r="AB17" t="n">
-        <v>67.74558053649058</v>
+        <v>67.74558053649056</v>
       </c>
       <c r="AC17" t="n">
-        <v>69.34814866059537</v>
+        <v>69.34814866059534</v>
       </c>
       <c r="AD17" t="n">
         <v>70.89994910704428</v>
       </c>
       <c r="AE17" t="n">
-        <v>72.45862989562971</v>
+        <v>72.4586298956297</v>
       </c>
       <c r="AF17" t="n">
-        <v>74.04176811983838</v>
+        <v>74.04176811983827</v>
       </c>
       <c r="AG17" t="n">
-        <v>75.65066143863132</v>
+        <v>75.65066143863118</v>
       </c>
       <c r="AH17" t="n">
-        <v>77.27845173859563</v>
+        <v>77.27845173859573</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.91460795471176</v>
+        <v>78.91460795471158</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>0.0469.3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10.63379254162596</v>
+        <v>10.63379254162597</v>
       </c>
       <c r="C18" t="n">
         <v>13.65600778512118</v>
@@ -2295,37 +2283,37 @@
         <v>16.66304289386548</v>
       </c>
       <c r="E18" t="n">
-        <v>19.64114523536245</v>
+        <v>19.64114523536246</v>
       </c>
       <c r="F18" t="n">
-        <v>22.58089307445633</v>
+        <v>22.58089307445634</v>
       </c>
       <c r="G18" t="n">
-        <v>25.48249215483532</v>
+        <v>25.48249215483533</v>
       </c>
       <c r="H18" t="n">
-        <v>28.36570547746251</v>
+        <v>28.3657054774625</v>
       </c>
       <c r="I18" t="n">
-        <v>31.29990318079831</v>
+        <v>31.29990318079832</v>
       </c>
       <c r="J18" t="n">
-        <v>33.89718144369492</v>
+        <v>33.89718144369494</v>
       </c>
       <c r="K18" t="n">
         <v>36.27363485262992</v>
       </c>
       <c r="L18" t="n">
-        <v>38.41235765775385</v>
+        <v>38.41235765775387</v>
       </c>
       <c r="M18" t="n">
-        <v>40.31770368746544</v>
+        <v>40.31770368746543</v>
       </c>
       <c r="N18" t="n">
         <v>41.96547773440157</v>
       </c>
       <c r="O18" t="n">
-        <v>43.39270913512101</v>
+        <v>43.392709135121</v>
       </c>
       <c r="P18" t="n">
         <v>44.66732015816818</v>
@@ -2340,7 +2328,7 @@
         <v>48.01773991408218</v>
       </c>
       <c r="T18" t="n">
-        <v>49.00968257594433</v>
+        <v>49.00968257594432</v>
       </c>
       <c r="U18" t="n">
         <v>49.94049417639379</v>
@@ -2352,77 +2340,77 @@
         <v>51.67107571115837</v>
       </c>
       <c r="X18" t="n">
-        <v>52.53771358122854</v>
+        <v>52.53771358122855</v>
       </c>
       <c r="Y18" t="n">
         <v>53.48429874001474</v>
       </c>
       <c r="Z18" t="n">
-        <v>54.56164002660335</v>
+        <v>54.56164002660334</v>
       </c>
       <c r="AA18" t="n">
         <v>55.76788356897335</v>
       </c>
       <c r="AB18" t="n">
-        <v>57.0570591602616</v>
+        <v>57.05705916026162</v>
       </c>
       <c r="AC18" t="n">
-        <v>58.50063899846474</v>
+        <v>58.50063899846473</v>
       </c>
       <c r="AD18" t="n">
         <v>59.93697777699067</v>
       </c>
       <c r="AE18" t="n">
-        <v>61.39309794540958</v>
+        <v>61.39309794540955</v>
       </c>
       <c r="AF18" t="n">
-        <v>62.87234849500847</v>
+        <v>62.87234849500851</v>
       </c>
       <c r="AG18" t="n">
-        <v>64.36947163560338</v>
+        <v>64.36947163560339</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.87610431158538</v>
+        <v>65.87610431158527</v>
       </c>
       <c r="AI18" t="n">
-        <v>67.38454577275586</v>
+        <v>67.384545772756</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>0.0469</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.411016415843652</v>
+        <v>5.41101641584362</v>
       </c>
       <c r="C19" t="n">
-        <v>8.507180625299881</v>
+        <v>8.507180625299869</v>
       </c>
       <c r="D19" t="n">
-        <v>11.61271768441851</v>
+        <v>11.6127176844185</v>
       </c>
       <c r="E19" t="n">
-        <v>14.71563337857788</v>
+        <v>14.71563337857786</v>
       </c>
       <c r="F19" t="n">
-        <v>17.80146776962622</v>
+        <v>17.80146776962621</v>
       </c>
       <c r="G19" t="n">
-        <v>20.86192354143986</v>
+        <v>20.86192354143985</v>
       </c>
       <c r="H19" t="n">
-        <v>23.90203048890276</v>
+        <v>23.90203048890275</v>
       </c>
       <c r="I19" t="n">
-        <v>26.95742479573658</v>
+        <v>26.95742479573657</v>
       </c>
       <c r="J19" t="n">
         <v>30.01094362231469</v>
       </c>
       <c r="K19" t="n">
-        <v>33.01201907441344</v>
+        <v>33.01201907441343</v>
       </c>
       <c r="L19" t="n">
         <v>35.83921937488188</v>
@@ -2431,7 +2419,7 @@
         <v>38.42104042997964</v>
       </c>
       <c r="N19" t="n">
-        <v>40.75555037220232</v>
+        <v>40.75555037220231</v>
       </c>
       <c r="O19" t="n">
         <v>42.86495215905958</v>
@@ -2443,83 +2431,83 @@
         <v>46.5603637362705</v>
       </c>
       <c r="R19" t="n">
-        <v>48.16956184809396</v>
+        <v>48.16956184809397</v>
       </c>
       <c r="S19" t="n">
         <v>49.62887604949228</v>
       </c>
       <c r="T19" t="n">
-        <v>50.94403760909723</v>
+        <v>50.94403760909724</v>
       </c>
       <c r="U19" t="n">
-        <v>52.12481245091287</v>
+        <v>52.12481245091288</v>
       </c>
       <c r="V19" t="n">
         <v>53.19323471021048</v>
       </c>
       <c r="W19" t="n">
-        <v>54.15184063119423</v>
+        <v>54.15184063119425</v>
       </c>
       <c r="X19" t="n">
-        <v>54.99910063951118</v>
+        <v>54.9991006395112</v>
       </c>
       <c r="Y19" t="n">
         <v>55.75015334391514</v>
       </c>
       <c r="Z19" t="n">
-        <v>56.4393801061685</v>
+        <v>56.43938010616851</v>
       </c>
       <c r="AA19" t="n">
-        <v>57.10680987515266</v>
+        <v>57.10680987515268</v>
       </c>
       <c r="AB19" t="n">
-        <v>57.78424736701004</v>
+        <v>57.78424736701005</v>
       </c>
       <c r="AC19" t="n">
         <v>58.5033294134805</v>
       </c>
       <c r="AD19" t="n">
-        <v>59.23145220697481</v>
+        <v>59.23145220697477</v>
       </c>
       <c r="AE19" t="n">
         <v>59.94997307583655</v>
       </c>
       <c r="AF19" t="n">
-        <v>60.66422412154238</v>
+        <v>60.66422412154228</v>
       </c>
       <c r="AG19" t="n">
-        <v>61.38297861232627</v>
+        <v>61.38297861232621</v>
       </c>
       <c r="AH19" t="n">
-        <v>62.11522854509671</v>
+        <v>62.1152285450967</v>
       </c>
       <c r="AI19" t="n">
-        <v>62.8681745557152</v>
+        <v>62.86817455571536</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>0.0234.1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.781864653154795</v>
+        <v>9.781864653154653</v>
       </c>
       <c r="C20" t="n">
-        <v>12.63592578024852</v>
+        <v>12.63592578024853</v>
       </c>
       <c r="D20" t="n">
-        <v>15.47583408753749</v>
+        <v>15.47583408753751</v>
       </c>
       <c r="E20" t="n">
-        <v>18.29793185044472</v>
+        <v>18.2979318504447</v>
       </c>
       <c r="F20" t="n">
         <v>21.09728293512288</v>
       </c>
       <c r="G20" t="n">
-        <v>23.86902807317959</v>
+        <v>23.8690280731796</v>
       </c>
       <c r="H20" t="n">
         <v>26.61428104670443</v>
@@ -2534,13 +2522,13 @@
         <v>34.4262648107288</v>
       </c>
       <c r="L20" t="n">
-        <v>36.74946058722493</v>
+        <v>36.74946058722492</v>
       </c>
       <c r="M20" t="n">
         <v>38.91970239008693</v>
       </c>
       <c r="N20" t="n">
-        <v>40.94297178743816</v>
+        <v>40.94297178743817</v>
       </c>
       <c r="O20" t="n">
         <v>42.82237024810877</v>
@@ -2549,34 +2537,34 @@
         <v>44.5629105075939</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.17796140361315</v>
+        <v>46.17796140361313</v>
       </c>
       <c r="R20" t="n">
-        <v>47.68142748678539</v>
+        <v>47.68142748678538</v>
       </c>
       <c r="S20" t="n">
-        <v>49.09196055528786</v>
+        <v>49.09196055528787</v>
       </c>
       <c r="T20" t="n">
         <v>50.42390428284934</v>
       </c>
       <c r="U20" t="n">
-        <v>51.68363424165264</v>
+        <v>51.68363424165265</v>
       </c>
       <c r="V20" t="n">
-        <v>52.87088727420021</v>
+        <v>52.87088727420019</v>
       </c>
       <c r="W20" t="n">
-        <v>53.99407743491459</v>
+        <v>53.99407743491458</v>
       </c>
       <c r="X20" t="n">
         <v>55.06965730837307</v>
       </c>
       <c r="Y20" t="n">
-        <v>56.11254759101269</v>
+        <v>56.11254759101267</v>
       </c>
       <c r="Z20" t="n">
-        <v>57.13436114847165</v>
+        <v>57.13436114847167</v>
       </c>
       <c r="AA20" t="n">
         <v>58.1469474049273</v>
@@ -2591,44 +2579,44 @@
         <v>61.17851015841858</v>
       </c>
       <c r="AE20" t="n">
-        <v>62.1880726762418</v>
+        <v>62.18807267624179</v>
       </c>
       <c r="AF20" t="n">
-        <v>63.20175732696065</v>
+        <v>63.20175732696059</v>
       </c>
       <c r="AG20" t="n">
-        <v>64.22300497345557</v>
+        <v>64.22300497345543</v>
       </c>
       <c r="AH20" t="n">
-        <v>65.25345036973275</v>
+        <v>65.2534503697327</v>
       </c>
       <c r="AI20" t="n">
-        <v>66.29262848542444</v>
+        <v>66.2926284854243</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>0.0234</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.873952453932574</v>
+        <v>2.873952453932559</v>
       </c>
       <c r="C21" t="n">
-        <v>6.249727334768874</v>
+        <v>6.249727334768871</v>
       </c>
       <c r="D21" t="n">
-        <v>9.625456631326387</v>
+        <v>9.625456631326379</v>
       </c>
       <c r="E21" t="n">
         <v>12.9843428860847</v>
       </c>
       <c r="F21" t="n">
-        <v>16.31315322956888</v>
+        <v>16.31315322956887</v>
       </c>
       <c r="G21" t="n">
-        <v>19.60865218276074</v>
+        <v>19.60865218276073</v>
       </c>
       <c r="H21" t="n">
         <v>22.88678210944792</v>
@@ -2643,7 +2631,7 @@
         <v>32.31538837044798</v>
       </c>
       <c r="L21" t="n">
-        <v>35.00967629970051</v>
+        <v>35.00967629970052</v>
       </c>
       <c r="M21" t="n">
         <v>37.42969912114154</v>
@@ -2655,22 +2643,22 @@
         <v>41.49266394519675</v>
       </c>
       <c r="P21" t="n">
-        <v>43.25839694948981</v>
+        <v>43.25839694948982</v>
       </c>
       <c r="Q21" t="n">
         <v>44.98435610023935</v>
       </c>
       <c r="R21" t="n">
-        <v>46.74807077371556</v>
+        <v>46.74807077371555</v>
       </c>
       <c r="S21" t="n">
-        <v>48.5708700368827</v>
+        <v>48.57087003688269</v>
       </c>
       <c r="T21" t="n">
         <v>50.444793883537</v>
       </c>
       <c r="U21" t="n">
-        <v>52.35620138152876</v>
+        <v>52.35620138152875</v>
       </c>
       <c r="V21" t="n">
         <v>54.31017093708584</v>
@@ -2679,19 +2667,19 @@
         <v>56.28486686355478</v>
       </c>
       <c r="X21" t="n">
-        <v>58.20656069910992</v>
+        <v>58.20656069910994</v>
       </c>
       <c r="Y21" t="n">
-        <v>59.99868223432217</v>
+        <v>59.9986822343222</v>
       </c>
       <c r="Z21" t="n">
-        <v>61.6382361649221</v>
+        <v>61.63823616492209</v>
       </c>
       <c r="AA21" t="n">
         <v>63.10450762432001</v>
       </c>
       <c r="AB21" t="n">
-        <v>64.31935694126213</v>
+        <v>64.31935694126216</v>
       </c>
       <c r="AC21" t="n">
         <v>64.98197979932257</v>
@@ -2700,38 +2688,38 @@
         <v>65.57506087628113</v>
       </c>
       <c r="AE21" t="n">
-        <v>66.13250211452097</v>
+        <v>66.13250211452099</v>
       </c>
       <c r="AF21" t="n">
-        <v>66.65685767554348</v>
+        <v>66.65685767554345</v>
       </c>
       <c r="AG21" t="n">
-        <v>67.14755982527639</v>
+        <v>67.1475598252764</v>
       </c>
       <c r="AH21" t="n">
-        <v>67.59997051991142</v>
+        <v>67.59997051991137</v>
       </c>
       <c r="AI21" t="n">
-        <v>68.00656132027231</v>
+        <v>68.00656132027224</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>0.0117.1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.933429995288375</v>
+        <v>4.933429995288378</v>
       </c>
       <c r="C22" t="n">
-        <v>7.92864827500263</v>
+        <v>7.928648275002643</v>
       </c>
       <c r="D22" t="n">
-        <v>10.94389010810695</v>
+        <v>10.94389010810697</v>
       </c>
       <c r="E22" t="n">
-        <v>13.97618850595849</v>
+        <v>13.9761885059585</v>
       </c>
       <c r="F22" t="n">
         <v>17.01982200536052</v>
@@ -2746,237 +2734,237 @@
         <v>26.20145222695927</v>
       </c>
       <c r="J22" t="n">
-        <v>29.19626036183731</v>
+        <v>29.1962603618373</v>
       </c>
       <c r="K22" t="n">
-        <v>32.0006232467324</v>
+        <v>32.00062324673239</v>
       </c>
       <c r="L22" t="n">
-        <v>34.61719184882404</v>
+        <v>34.61719184882406</v>
       </c>
       <c r="M22" t="n">
         <v>37.07742527151706</v>
       </c>
       <c r="N22" t="n">
-        <v>39.40082884961797</v>
+        <v>39.40082884961796</v>
       </c>
       <c r="O22" t="n">
-        <v>41.58980270093895</v>
+        <v>41.58980270093896</v>
       </c>
       <c r="P22" t="n">
-        <v>43.62239637302419</v>
+        <v>43.6223963730242</v>
       </c>
       <c r="Q22" t="n">
-        <v>45.45212423180132</v>
+        <v>45.45212423180133</v>
       </c>
       <c r="R22" t="n">
-        <v>47.05791219005875</v>
+        <v>47.05791219005872</v>
       </c>
       <c r="S22" t="n">
-        <v>48.52009701735455</v>
+        <v>48.52009701735457</v>
       </c>
       <c r="T22" t="n">
-        <v>49.95141908385502</v>
+        <v>49.95141908385503</v>
       </c>
       <c r="U22" t="n">
-        <v>51.39119868236346</v>
+        <v>51.39119868236347</v>
       </c>
       <c r="V22" t="n">
-        <v>52.81830610336107</v>
+        <v>52.81830610336104</v>
       </c>
       <c r="W22" t="n">
-        <v>54.19123994678739</v>
+        <v>54.19123994678737</v>
       </c>
       <c r="X22" t="n">
-        <v>55.46714863193545</v>
+        <v>55.46714863193544</v>
       </c>
       <c r="Y22" t="n">
-        <v>56.63387230375237</v>
+        <v>56.63387230375238</v>
       </c>
       <c r="Z22" t="n">
-        <v>57.68327765317094</v>
+        <v>57.68327765317095</v>
       </c>
       <c r="AA22" t="n">
-        <v>58.61764770285513</v>
+        <v>58.61764770285512</v>
       </c>
       <c r="AB22" t="n">
-        <v>59.42382904921517</v>
+        <v>59.42382904921516</v>
       </c>
       <c r="AC22" t="n">
         <v>59.91222457544409</v>
       </c>
       <c r="AD22" t="n">
-        <v>60.37318626731825</v>
+        <v>60.37318626731822</v>
       </c>
       <c r="AE22" t="n">
-        <v>60.81131484177477</v>
+        <v>60.81131484177475</v>
       </c>
       <c r="AF22" t="n">
         <v>61.22755271626835</v>
       </c>
       <c r="AG22" t="n">
-        <v>61.62262668677598</v>
+        <v>61.62262668677605</v>
       </c>
       <c r="AH22" t="n">
-        <v>61.99746208223307</v>
+        <v>61.99746208223289</v>
       </c>
       <c r="AI22" t="n">
-        <v>62.35220358503842</v>
+        <v>62.35220358503822</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>0.0117.2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>37.68857738801754</v>
+        <v>33.35521571157175</v>
       </c>
       <c r="C23" t="n">
-        <v>37.4881035427638</v>
+        <v>34.32282413372374</v>
       </c>
       <c r="D23" t="n">
-        <v>37.29012490521656</v>
+        <v>35.23573003562716</v>
       </c>
       <c r="E23" t="n">
-        <v>37.09494298691413</v>
+        <v>36.09524718870384</v>
       </c>
       <c r="F23" t="n">
-        <v>36.90206578906848</v>
+        <v>36.90206578906849</v>
       </c>
       <c r="G23" t="n">
-        <v>36.70997145047355</v>
+        <v>36.70997145047357</v>
       </c>
       <c r="H23" t="n">
-        <v>36.51789291289346</v>
+        <v>36.51789291289347</v>
       </c>
       <c r="I23" t="n">
         <v>36.32373508209698</v>
       </c>
       <c r="J23" t="n">
-        <v>36.16754303209112</v>
+        <v>36.1675430320911</v>
       </c>
       <c r="K23" t="n">
-        <v>36.17015907379581</v>
+        <v>36.17015907379583</v>
       </c>
       <c r="L23" t="n">
-        <v>36.38309382164658</v>
+        <v>36.3830938216466</v>
       </c>
       <c r="M23" t="n">
-        <v>36.76358376919695</v>
+        <v>36.76358376919696</v>
       </c>
       <c r="N23" t="n">
-        <v>37.23482341986754</v>
+        <v>37.23482341986755</v>
       </c>
       <c r="O23" t="n">
-        <v>37.76160140872415</v>
+        <v>37.76160140872418</v>
       </c>
       <c r="P23" t="n">
-        <v>38.32621861205153</v>
+        <v>38.32621861205154</v>
       </c>
       <c r="Q23" t="n">
         <v>38.93508926088234</v>
       </c>
       <c r="R23" t="n">
-        <v>39.62538367863832</v>
+        <v>39.62538367863831</v>
       </c>
       <c r="S23" t="n">
-        <v>40.42681932871961</v>
+        <v>40.42681932871963</v>
       </c>
       <c r="T23" t="n">
-        <v>41.25512138712922</v>
+        <v>41.25512138712921</v>
       </c>
       <c r="U23" t="n">
-        <v>42.01983740165245</v>
+        <v>42.01983740165247</v>
       </c>
       <c r="V23" t="n">
         <v>42.72095030242641</v>
       </c>
       <c r="W23" t="n">
-        <v>43.36805351545031</v>
+        <v>43.36805351545032</v>
       </c>
       <c r="X23" t="n">
-        <v>43.9701538151015</v>
+        <v>43.97015381510148</v>
       </c>
       <c r="Y23" t="n">
-        <v>44.55523443792386</v>
+        <v>44.55523443792387</v>
       </c>
       <c r="Z23" t="n">
-        <v>45.14042278618571</v>
+        <v>45.14042278618572</v>
       </c>
       <c r="AA23" t="n">
-        <v>45.71323917654625</v>
+        <v>45.71323917654626</v>
       </c>
       <c r="AB23" t="n">
-        <v>46.26743746390006</v>
+        <v>46.26743746390005</v>
       </c>
       <c r="AC23" t="n">
         <v>46.75091109608277</v>
       </c>
       <c r="AD23" t="n">
-        <v>47.2191673328624</v>
+        <v>47.21916733286241</v>
       </c>
       <c r="AE23" t="n">
-        <v>47.68159689385954</v>
+        <v>47.68159689385952</v>
       </c>
       <c r="AF23" t="n">
-        <v>48.13844391096573</v>
+        <v>48.13844391096575</v>
       </c>
       <c r="AG23" t="n">
-        <v>48.58824277175366</v>
+        <v>48.58824277175362</v>
       </c>
       <c r="AH23" t="n">
-        <v>49.02852044477544</v>
+        <v>49.02852044477552</v>
       </c>
       <c r="AI23" t="n">
-        <v>49.45793659350666</v>
+        <v>49.45793659350662</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>0.0117</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.36729747752177</v>
+        <v>10.36729747752178</v>
       </c>
       <c r="C24" t="n">
-        <v>12.92458410031004</v>
+        <v>12.92458410031003</v>
       </c>
       <c r="D24" t="n">
-        <v>15.46510768779885</v>
+        <v>15.46510768779889</v>
       </c>
       <c r="E24" t="n">
-        <v>17.98185636672176</v>
+        <v>17.98185636672178</v>
       </c>
       <c r="F24" t="n">
-        <v>20.47240595135291</v>
+        <v>20.47240595135294</v>
       </c>
       <c r="G24" t="n">
-        <v>22.94156027091972</v>
+        <v>22.94156027091976</v>
       </c>
       <c r="H24" t="n">
-        <v>25.40655582687122</v>
+        <v>25.40655582687126</v>
       </c>
       <c r="I24" t="n">
-        <v>27.91203389528571</v>
+        <v>27.91203389528576</v>
       </c>
       <c r="J24" t="n">
-        <v>30.15806064651484</v>
+        <v>30.15806064651488</v>
       </c>
       <c r="K24" t="n">
-        <v>32.22984555212437</v>
+        <v>32.22984555212441</v>
       </c>
       <c r="L24" t="n">
         <v>34.10093401206314</v>
       </c>
       <c r="M24" t="n">
-        <v>35.74429197335652</v>
+        <v>35.7442919733565</v>
       </c>
       <c r="N24" t="n">
-        <v>37.16856921510735</v>
+        <v>37.16856921510734</v>
       </c>
       <c r="O24" t="n">
         <v>38.44086253465468</v>
@@ -2988,58 +2976,58 @@
         <v>40.71932392717561</v>
       </c>
       <c r="R24" t="n">
-        <v>41.74396574560993</v>
+        <v>41.74396574560994</v>
       </c>
       <c r="S24" t="n">
-        <v>42.69710754945095</v>
+        <v>42.69710754945098</v>
       </c>
       <c r="T24" t="n">
-        <v>43.57193642466586</v>
+        <v>43.57193642466591</v>
       </c>
       <c r="U24" t="n">
-        <v>44.36334696371387</v>
+        <v>44.36334696371391</v>
       </c>
       <c r="V24" t="n">
-        <v>45.08438369912706</v>
+        <v>45.0843836991271</v>
       </c>
       <c r="W24" t="n">
-        <v>45.75749299092859</v>
+        <v>45.75749299092864</v>
       </c>
       <c r="X24" t="n">
-        <v>46.39911368145506</v>
+        <v>46.39911368145509</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.02826081417667</v>
+        <v>47.0282608141767</v>
       </c>
       <c r="Z24" t="n">
-        <v>47.63509620447292</v>
+        <v>47.63509620447295</v>
       </c>
       <c r="AA24" t="n">
-        <v>48.19319243260532</v>
+        <v>48.19319243260534</v>
       </c>
       <c r="AB24" t="n">
         <v>48.69762466824174</v>
       </c>
       <c r="AC24" t="n">
-        <v>49.18576667682446</v>
+        <v>49.18576667682447</v>
       </c>
       <c r="AD24" t="n">
-        <v>49.66817362116979</v>
+        <v>49.66817362116982</v>
       </c>
       <c r="AE24" t="n">
         <v>50.15309968384445</v>
       </c>
       <c r="AF24" t="n">
-        <v>50.64247855515897</v>
+        <v>50.64247855515895</v>
       </c>
       <c r="AG24" t="n">
-        <v>51.13504775969567</v>
+        <v>51.13504775969575</v>
       </c>
       <c r="AH24" t="n">
-        <v>51.62864147303262</v>
+        <v>51.62864147303264</v>
       </c>
       <c r="AI24" t="n">
-        <v>52.12145581796585</v>
+        <v>52.12145581796576</v>
       </c>
     </row>
   </sheetData>
@@ -3057,509 +3045,509 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_0.00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_0.97</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_1.94</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>t_2.91</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_3.88</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>t_4.85</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>t_5.82</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>t_6.79</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>t_7.76</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>t_8.73</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>t_9.70</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>t_10.67</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>t_11.64</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>t_12.61</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>t_13.58</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>t_14.55</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>t_15.52</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>t_16.48</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>t_17.45</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>t_18.42</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>t_19.39</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>t_20.36</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>t_21.33</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>t_22.30</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>t_23.27</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>t_24.24</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>t_25.21</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>t_26.18</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>t_27.15</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>t_28.12</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>t_29.09</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>t_30.06</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>t_31.03</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>t_32.00</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>t_32.97</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>t_33.94</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>t_34.91</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>t_35.88</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>t_36.85</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>t_37.82</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>t_38.79</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>t_39.76</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>t_40.73</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>t_41.70</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>t_42.67</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>t_43.64</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>t_44.61</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>t_45.58</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>t_46.55</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>t_47.52</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>t_48.48</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>t_49.45</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>t_50.42</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>t_51.39</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>t_52.36</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>t_53.33</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>t_54.30</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>t_55.27</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>t_56.24</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>t_57.21</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>t_58.18</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>t_59.15</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>t_60.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>t_61.09</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>t_62.06</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>t_63.03</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>t_64.00</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>t_64.97</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>t_65.94</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>t_66.91</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>t_67.88</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>t_68.85</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>t_69.82</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>t_70.79</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>t_71.76</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>t_72.73</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>t_73.70</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>t_74.67</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>t_75.64</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>t_76.61</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>t_77.58</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>t_78.55</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>t_79.52</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>t_80.48</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>t_81.45</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>t_82.42</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>t_83.39</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>t_84.36</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>t_85.33</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>t_86.30</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>t_87.27</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>t_88.24</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>t_89.21</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>t_90.18</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>t_91.15</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>t_92.12</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>t_93.09</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>t_94.06</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>t_95.03</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>t_96.00</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>dr_0.0000</t>
         </is>
@@ -3866,7 +3854,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>dr_0.0202</t>
         </is>
@@ -4173,7 +4161,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>dr_0.0404</t>
         </is>
@@ -4480,7 +4468,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>dr_0.0606</t>
         </is>
@@ -4787,7 +4775,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>dr_0.0808</t>
         </is>
@@ -5094,7 +5082,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>dr_0.1010</t>
         </is>
@@ -5401,7 +5389,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>dr_0.1212</t>
         </is>
@@ -5708,7 +5696,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>dr_0.1414</t>
         </is>
@@ -6015,7 +6003,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>dr_0.1616</t>
         </is>
@@ -6322,7 +6310,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>dr_0.1818</t>
         </is>
@@ -6629,7 +6617,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>dr_0.2020</t>
         </is>
@@ -6936,7 +6924,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>dr_0.2222</t>
         </is>
@@ -7243,7 +7231,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>dr_0.2424</t>
         </is>
@@ -7550,7 +7538,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>dr_0.2626</t>
         </is>
@@ -7857,7 +7845,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>dr_0.2828</t>
         </is>
@@ -8164,7 +8152,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>dr_0.3030</t>
         </is>
@@ -8471,7 +8459,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>dr_0.3232</t>
         </is>
@@ -8778,7 +8766,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>dr_0.3434</t>
         </is>
@@ -9085,7 +9073,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>dr_0.3636</t>
         </is>
@@ -9392,7 +9380,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>dr_0.3838</t>
         </is>
@@ -9699,7 +9687,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>dr_0.4040</t>
         </is>
@@ -10006,7 +9994,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>dr_0.4242</t>
         </is>
@@ -10313,7 +10301,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>dr_0.4444</t>
         </is>
@@ -10620,7 +10608,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>dr_0.4646</t>
         </is>
@@ -10927,7 +10915,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>dr_0.4848</t>
         </is>
@@ -11234,7 +11222,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>dr_0.5051</t>
         </is>
@@ -11541,7 +11529,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>dr_0.5253</t>
         </is>
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>dr_0.5455</t>
         </is>
@@ -12155,7 +12143,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>dr_0.5657</t>
         </is>
@@ -12462,7 +12450,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>dr_0.5859</t>
         </is>
@@ -12769,7 +12757,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>dr_0.6061</t>
         </is>
@@ -13076,7 +13064,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>dr_0.6263</t>
         </is>
@@ -13383,7 +13371,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>dr_0.6465</t>
         </is>
@@ -13690,7 +13678,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>dr_0.6667</t>
         </is>
@@ -13997,7 +13985,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>dr_0.6869</t>
         </is>
@@ -14304,7 +14292,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>dr_0.7071</t>
         </is>
@@ -14611,7 +14599,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>dr_0.7273</t>
         </is>
@@ -14918,7 +14906,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>dr_0.7475</t>
         </is>
@@ -15225,7 +15213,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>dr_0.7677</t>
         </is>
@@ -15532,7 +15520,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>dr_0.7879</t>
         </is>
@@ -15839,7 +15827,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>dr_0.8081</t>
         </is>
@@ -16146,7 +16134,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>dr_0.8283</t>
         </is>
@@ -16453,7 +16441,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>dr_0.8485</t>
         </is>
@@ -16760,7 +16748,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>dr_0.8687</t>
         </is>
@@ -17067,7 +17055,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>dr_0.8889</t>
         </is>
@@ -17374,7 +17362,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>dr_0.9091</t>
         </is>
@@ -17681,7 +17669,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>dr_0.9293</t>
         </is>
@@ -17988,7 +17976,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>dr_0.9495</t>
         </is>
@@ -18295,7 +18283,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>dr_0.9697</t>
         </is>
@@ -18602,7 +18590,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>dr_0.9899</t>
         </is>
@@ -18909,7 +18897,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>dr_1.0101</t>
         </is>
@@ -19216,7 +19204,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>dr_1.0303</t>
         </is>
@@ -19523,7 +19511,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>dr_1.0505</t>
         </is>
@@ -19830,7 +19818,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>dr_1.0707</t>
         </is>
@@ -20137,7 +20125,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>dr_1.0909</t>
         </is>
@@ -20444,7 +20432,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>dr_1.1111</t>
         </is>
@@ -20751,7 +20739,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>dr_1.1313</t>
         </is>
@@ -21058,7 +21046,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>dr_1.1515</t>
         </is>
@@ -21365,7 +21353,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>dr_1.1717</t>
         </is>
@@ -21672,7 +21660,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>dr_1.1919</t>
         </is>
@@ -21979,7 +21967,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>dr_1.2121</t>
         </is>
@@ -22286,7 +22274,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>dr_1.2323</t>
         </is>
@@ -22593,7 +22581,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>dr_1.2525</t>
         </is>
@@ -22900,7 +22888,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>dr_1.2727</t>
         </is>
@@ -23207,7 +23195,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>dr_1.2929</t>
         </is>
@@ -23514,7 +23502,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>dr_1.3131</t>
         </is>
@@ -23821,7 +23809,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>dr_1.3333</t>
         </is>
@@ -24128,7 +24116,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>dr_1.3535</t>
         </is>
@@ -24435,7 +24423,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>dr_1.3737</t>
         </is>
@@ -24742,7 +24730,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>dr_1.3939</t>
         </is>
@@ -25049,7 +25037,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>dr_1.4141</t>
         </is>
@@ -25356,7 +25344,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>dr_1.4343</t>
         </is>
@@ -25663,7 +25651,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>dr_1.4545</t>
         </is>
@@ -25970,7 +25958,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>dr_1.4747</t>
         </is>
@@ -26277,7 +26265,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>dr_1.4949</t>
         </is>
@@ -26584,7 +26572,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>dr_1.5152</t>
         </is>
@@ -26891,7 +26879,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>dr_1.5354</t>
         </is>
@@ -27198,7 +27186,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>dr_1.5556</t>
         </is>
@@ -27505,7 +27493,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>dr_1.5758</t>
         </is>
@@ -27812,7 +27800,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>dr_1.5960</t>
         </is>
@@ -28119,7 +28107,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>dr_1.6162</t>
         </is>
@@ -28426,7 +28414,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>dr_1.6364</t>
         </is>
@@ -28733,7 +28721,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>dr_1.6566</t>
         </is>
@@ -29040,7 +29028,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>dr_1.6768</t>
         </is>
@@ -29347,7 +29335,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>dr_1.6970</t>
         </is>
@@ -29654,7 +29642,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>dr_1.7172</t>
         </is>
@@ -29961,7 +29949,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>dr_1.7374</t>
         </is>
@@ -30268,7 +30256,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>dr_1.7576</t>
         </is>
@@ -30575,7 +30563,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>dr_1.7778</t>
         </is>
@@ -30882,7 +30870,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>dr_1.7980</t>
         </is>
@@ -31189,7 +31177,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>dr_1.8182</t>
         </is>
@@ -31496,7 +31484,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>dr_1.8384</t>
         </is>
@@ -31803,7 +31791,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>dr_1.8586</t>
         </is>
@@ -32110,7 +32098,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>dr_1.8788</t>
         </is>
@@ -32417,7 +32405,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>dr_1.8990</t>
         </is>
@@ -32724,7 +32712,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>dr_1.9192</t>
         </is>
@@ -33031,7 +33019,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>dr_1.9394</t>
         </is>
@@ -33338,7 +33326,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>dr_1.9596</t>
         </is>
@@ -33645,7 +33633,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>dr_1.9798</t>
         </is>
@@ -33952,7 +33940,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>dr_2.0000</t>
         </is>
@@ -34273,62 +34261,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>equation</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>drug</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>R0_O2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Emax_O2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mu_c_O2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sigma_c_O2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>tau_O2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>m_O2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>E_tox_O2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>n_O2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TC50_norm_O2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>tau_tox_O2</t>
         </is>
@@ -34391,27 +34379,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Heatmap_Source</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Coefficient_Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pipeline</t>
         </is>
@@ -34420,12 +34408,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\Heatmaps\Dactinomycin\O2_mean_sorted.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/Heatmaps/Dactinomycin/O2_mean_sorted.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\EQN_Coefficients\all_equations_coefficients.xlsx</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/EQN_Coefficients/all_equations_coefficients.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
